--- a/uploads/archive/MKU 8.xlsx
+++ b/uploads/archive/MKU 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\file rendy\DATA KIRIMAN\MKU\2026\8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\file rendy\DATA KIRIMAN\MKU\2026\9\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$L$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$L$150</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="396">
   <si>
     <t>No. Urut</t>
   </si>
@@ -60,43 +60,1042 @@
     <t>Qty BS</t>
   </si>
   <si>
-    <t>SO-KU/2608/070001</t>
+    <t>SO-KU/2609/070002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Seminyak </t>
+  </si>
+  <si>
+    <t>DRY</t>
+  </si>
+  <si>
+    <t>PT LAPLANCHA BALI SEJAHTERA</t>
+  </si>
+  <si>
+    <t>Sujana</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>POS0026</t>
+  </si>
+  <si>
+    <t>O Sole Olive Nere Denocciolate 4.1 Kg</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denpasar  - Barat </t>
+  </si>
+  <si>
+    <t>FROZEN</t>
+  </si>
+  <si>
+    <t>NDEUZZ FROZEN FOOD</t>
+  </si>
+  <si>
+    <t>Ni Ketut Sriasih (GT)</t>
+  </si>
+  <si>
+    <t>PSJ0019</t>
+  </si>
+  <si>
+    <t>Pork B Sliced (1kg/pack)</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070005</t>
+  </si>
+  <si>
+    <t>DJAYA DELAPAN COFFEE</t>
+  </si>
+  <si>
+    <t>I MADE LUIH</t>
+  </si>
+  <si>
+    <t>PMS0094</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Butterscotch 850 Ml</t>
+  </si>
+  <si>
+    <t>BTL</t>
+  </si>
+  <si>
+    <t>PMS0130</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Classic Caramel 850ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070006</t>
   </si>
   <si>
     <t>Denpasar  - Utara</t>
   </si>
   <si>
-    <t>FROZEN</t>
+    <t>VIBES</t>
+  </si>
+  <si>
+    <t>PMS0027</t>
+  </si>
+  <si>
+    <t>Masterista Red Velvet Expecta 800Gr</t>
+  </si>
+  <si>
+    <t>POU</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denpasar  - Selatan </t>
+  </si>
+  <si>
+    <t>ASA COFFEE RESTO</t>
+  </si>
+  <si>
+    <t>PMS0031</t>
+  </si>
+  <si>
+    <t>Masterista Aren Sugar Liquid 1000Gr</t>
+  </si>
+  <si>
+    <t>PMS0039</t>
+  </si>
+  <si>
+    <t>Flavorista Matcha (1000Gr/Pack)</t>
+  </si>
+  <si>
+    <t>PACK</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070008</t>
+  </si>
+  <si>
+    <t>MURAH SOSIS TRENGGANA</t>
+  </si>
+  <si>
+    <t>PSJ0020</t>
+  </si>
+  <si>
+    <t>Off Cut 500 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Canggu </t>
+  </si>
+  <si>
+    <t>TRIPLE EGG RESTAURANT</t>
+  </si>
+  <si>
+    <t>Taufik</t>
+  </si>
+  <si>
+    <t>PMS0178</t>
+  </si>
+  <si>
+    <t>Masterista Ceremonial Pure Matcha Powder 500 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070010</t>
+  </si>
+  <si>
+    <t>FUCINA ITALIA</t>
+  </si>
+  <si>
+    <t>Dewi Kristiani</t>
+  </si>
+  <si>
+    <t>POT0034</t>
+  </si>
+  <si>
+    <t>Premium Straight Cut 6x2Kg</t>
+  </si>
+  <si>
+    <t>KTN</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070011</t>
+  </si>
+  <si>
+    <t>PT. AMAN BALI NUSA LAUT (LUIGIS HOT PIZZA)</t>
+  </si>
+  <si>
+    <t>POS0024</t>
+  </si>
+  <si>
+    <t>O Sole Pomodori Pelati Peeled Tomatoes 2.5Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070012</t>
+  </si>
+  <si>
+    <t>DAPUR SEMBILAN FROZEN FOOD</t>
+  </si>
+  <si>
+    <t>Wira</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070013</t>
+  </si>
+  <si>
+    <t>METLAND SEVA SEMINYAK</t>
+  </si>
+  <si>
+    <t>Vacant Hotel Kuta Seminyak</t>
+  </si>
+  <si>
+    <t>PIF0012</t>
+  </si>
+  <si>
+    <t>Pristine Classic Cooking Cream 1 Lt</t>
+  </si>
+  <si>
+    <t>LTR</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070014</t>
+  </si>
+  <si>
+    <t>CAPRI BALI</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070015</t>
+  </si>
+  <si>
+    <t>COFFEE CARTEL</t>
+  </si>
+  <si>
+    <t>POT0156</t>
+  </si>
+  <si>
+    <t>Premium Hash Brown 2.5Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070016</t>
+  </si>
+  <si>
+    <t>LE CROISSANT</t>
+  </si>
+  <si>
+    <t>PMS0026</t>
+  </si>
+  <si>
+    <t>Masterista Dark Chocolate 800Gr</t>
+  </si>
+  <si>
+    <t>PMS0131</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Tropical Lychee 850 Ml</t>
+  </si>
+  <si>
+    <t>PMS0132</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Vanilla Tradition 850ml</t>
+  </si>
+  <si>
+    <t>PMS0144</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Peach 850ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Kuta </t>
+  </si>
+  <si>
+    <t>ZEEN COFFEE</t>
+  </si>
+  <si>
+    <t>PMS0037</t>
+  </si>
+  <si>
+    <t>Flavorista Red Velvet (1000Gr/Pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070018</t>
   </si>
   <si>
     <t>MB FROZEN FOOD</t>
   </si>
   <si>
-    <t>Ni Ketut Sriasih (GT)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>PSJ0019</t>
-  </si>
-  <si>
-    <t>Pork B Sliced (1kg/pack)</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Seminyak </t>
-  </si>
-  <si>
-    <t>ZIA TINA BALI</t>
-  </si>
-  <si>
-    <t>Sujana</t>
+    <t>SO-KU/2609/070019</t>
+  </si>
+  <si>
+    <t>JFC PIDADA</t>
+  </si>
+  <si>
+    <t>PMS0040</t>
+  </si>
+  <si>
+    <t>Flavorista Taro (1000Gr/Pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070020</t>
+  </si>
+  <si>
+    <t>BUZO RESTAURANT</t>
+  </si>
+  <si>
+    <t>ASS-EGT</t>
+  </si>
+  <si>
+    <t>Earl Grey @50TB/Box</t>
+  </si>
+  <si>
+    <t>BOX</t>
+  </si>
+  <si>
+    <t>ASS-JVJ</t>
+  </si>
+  <si>
+    <t>Javanese Jasmine Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>ASS-PGT</t>
+  </si>
+  <si>
+    <t>Pure Green Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070021</t>
+  </si>
+  <si>
+    <t>DOM BY DOPPIO</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070022</t>
+  </si>
+  <si>
+    <t>TRAYA COFFEE</t>
+  </si>
+  <si>
+    <t>PMS0059</t>
+  </si>
+  <si>
+    <t>Flavour Artisan - Belgian Signature Dark Chocolate (80 Cocoa%)  500gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070024</t>
+  </si>
+  <si>
+    <t>SANDI WIJAYA</t>
+  </si>
+  <si>
+    <t>Ni Ketut Sriasih (MT)</t>
+  </si>
+  <si>
+    <t>ASS-LY-TB10</t>
+  </si>
+  <si>
+    <t>Lychee Tea @10tb/pack</t>
+  </si>
+  <si>
+    <t>ASS-MO-TB10</t>
+  </si>
+  <si>
+    <t>Manggo Tea @10tb/pack</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070025</t>
+  </si>
+  <si>
+    <t>BADUNG  - Jimbaran Uluwatu</t>
+  </si>
+  <si>
+    <t>LA BRASSERIE JIMBARAN</t>
+  </si>
+  <si>
+    <t>Juni</t>
+  </si>
+  <si>
+    <t>PAS0062</t>
+  </si>
+  <si>
+    <t>Savis Cold Infusions Energizing 50Pbx4g</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070026</t>
+  </si>
+  <si>
+    <t>NAUGHTY NURIS SEMINYAK</t>
+  </si>
+  <si>
+    <t>NN Sujana</t>
+  </si>
+  <si>
+    <t>PSJ0029</t>
+  </si>
+  <si>
+    <t>Iga Babi</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070027</t>
+  </si>
+  <si>
+    <t>AMOLAS CAFE</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070028</t>
+  </si>
+  <si>
+    <t>Denpasar  - Sanur, Ketewel</t>
+  </si>
+  <si>
+    <t>NAUGHTY NURIS SANUR</t>
+  </si>
+  <si>
+    <t>NN Made Luih</t>
+  </si>
+  <si>
+    <t>PSJ0026</t>
+  </si>
+  <si>
+    <t>Samcan Babi Tanpa Kulit</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070029</t>
+  </si>
+  <si>
+    <t>WARUNG LOKAL</t>
+  </si>
+  <si>
+    <t>POT0038</t>
+  </si>
+  <si>
+    <t>Premium Straight Cut 2Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070030</t>
+  </si>
+  <si>
+    <t>CAVO BAR &amp; BISTRO</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070031</t>
+  </si>
+  <si>
+    <t>PADANG PADANG MART</t>
+  </si>
+  <si>
+    <t>CKP1S-159</t>
+  </si>
+  <si>
+    <t>Daebak Soju Lemon @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-160</t>
+  </si>
+  <si>
+    <t>Daebak Soju Mango @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-163</t>
+  </si>
+  <si>
+    <t>Daebak Soju Peach @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-164</t>
+  </si>
+  <si>
+    <t>Daebak Soju Lychee @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-165</t>
+  </si>
+  <si>
+    <t>Daebak Soju Original 360ml</t>
+  </si>
+  <si>
+    <t>CKP1S-181</t>
+  </si>
+  <si>
+    <t>Daebak Soju Grape 360ml</t>
+  </si>
+  <si>
+    <t>PJS0005</t>
+  </si>
+  <si>
+    <t>Daebak Spark Ice Lemon Tea 330 Ml</t>
+  </si>
+  <si>
+    <t>PJS0006</t>
+  </si>
+  <si>
+    <t>Daebak Spark Blood Orange 330 Ml</t>
+  </si>
+  <si>
+    <t>PJS0007</t>
+  </si>
+  <si>
+    <t>Daebak Spark Grape 330 Ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070032</t>
+  </si>
+  <si>
+    <t>ALILA HOTEL SEMINYAK</t>
+  </si>
+  <si>
+    <t>PAS0047</t>
+  </si>
+  <si>
+    <t>Savis Pure Bunga Telang 200 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070033</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East Bali  - Bangli </t>
+  </si>
+  <si>
+    <t>OCULUS HOTEL KINTAMANI</t>
+  </si>
+  <si>
+    <t>Picrom Stalyon</t>
+  </si>
+  <si>
+    <t>ASS-PE-TB50</t>
+  </si>
+  <si>
+    <t>Peppermint Tea @50tb/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070035</t>
+  </si>
+  <si>
+    <t>PMS0134</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Salted Caramel 850 ML</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070036</t>
+  </si>
+  <si>
+    <t>PT. SSP TAURUS GEMILANG INDONESIA</t>
+  </si>
+  <si>
+    <t>Wahyu</t>
+  </si>
+  <si>
+    <t>PEA0010</t>
+  </si>
+  <si>
+    <t>Gold Box Extra Butter MP341 1 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070037</t>
+  </si>
+  <si>
+    <t>ASS-CH-L250</t>
+  </si>
+  <si>
+    <t>Chamomile Dream @250gr</t>
+  </si>
+  <si>
+    <t>ASS-EG-LP250</t>
+  </si>
+  <si>
+    <t>Earl Grey @250gr</t>
+  </si>
+  <si>
+    <t>ASS-JT-LP250</t>
+  </si>
+  <si>
+    <t>Jasmine Tea @250gr/Pouch</t>
+  </si>
+  <si>
+    <t>ASS-PL-LP250</t>
+  </si>
+  <si>
+    <t>Lemongrass @250gr</t>
+  </si>
+  <si>
+    <t>ASS-PP-LP250</t>
+  </si>
+  <si>
+    <t>Peppermint @250gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070038</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070039</t>
+  </si>
+  <si>
+    <t>CENTRAL KITCHEN LOSTERIA (CANGGU)</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070040</t>
+  </si>
+  <si>
+    <t>BELLA ITALIAN GRAND MAS</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070041</t>
+  </si>
+  <si>
+    <t>BALI CATERING COMPANY</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070042</t>
+  </si>
+  <si>
+    <t>FINNS BEACH CLUB</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070043</t>
+  </si>
+  <si>
+    <t>BHIMA JAYA</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070044</t>
+  </si>
+  <si>
+    <t>Gianyar  - Gianyar</t>
+  </si>
+  <si>
+    <t>MAE RESTO GIANYAR</t>
+  </si>
+  <si>
+    <t>PMS0024</t>
+  </si>
+  <si>
+    <t>Masterista Original Matcha 800Gr</t>
+  </si>
+  <si>
+    <t>PMS0093</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Strawberry 850 Ml</t>
+  </si>
+  <si>
+    <t>PMS0150</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Natural Mint 850 Ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070045</t>
+  </si>
+  <si>
+    <t>ALAM CALDERA  CAMP RESTO KINTAMANI</t>
+  </si>
+  <si>
+    <t>MRD1318A</t>
+  </si>
+  <si>
+    <t>MAMAS BELLY RIND ON SB OUT (SKIN ON) 3-5KG/PACK</t>
+  </si>
+  <si>
+    <t>PAA0001</t>
+  </si>
+  <si>
+    <t>Bergold Mozzarella Block</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070046</t>
+  </si>
+  <si>
+    <t>AUTOGRILL</t>
+  </si>
+  <si>
+    <t>PSJ0032</t>
+  </si>
+  <si>
+    <t>Selecta Pork Belly Skin On</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070047</t>
+  </si>
+  <si>
+    <t>LOSTERIA LABUAN SAIT</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070048</t>
+  </si>
+  <si>
+    <t>PAS0012</t>
+  </si>
+  <si>
+    <t>Savis Organic Olong @250 GR</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070049</t>
+  </si>
+  <si>
+    <t>BADUNG  - NusaDua</t>
+  </si>
+  <si>
+    <t>NUSA DUA BEACH HOTEL</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>PQW0010</t>
+  </si>
+  <si>
+    <t>IQF FF Shoestring 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070050</t>
+  </si>
+  <si>
+    <t>Gianyar  - Ubud</t>
+  </si>
+  <si>
+    <t>FOLD UBUD</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070051</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070052</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East Bali  - Klungkung </t>
+  </si>
+  <si>
+    <t>GEP'S DELI ( TOKO SURYANTI NUSA )</t>
+  </si>
+  <si>
+    <t>PQW0012</t>
+  </si>
+  <si>
+    <t>IQF FF Shoestring 2.5 Kg/Pack</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070054</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070055</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070056</t>
+  </si>
+  <si>
+    <t>THE UDAYA RESORT</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070058</t>
+  </si>
+  <si>
+    <t>W HOTEL</t>
+  </si>
+  <si>
+    <t>PAS0007</t>
+  </si>
+  <si>
+    <t>Savis Green Tea 250Gr/Pack</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070059</t>
+  </si>
+  <si>
+    <t>WIRMA RESELLER</t>
+  </si>
+  <si>
+    <t>PMS0033</t>
+  </si>
+  <si>
+    <t>Masterista Ice Shaken Lemon Tea 1000Gr</t>
+  </si>
+  <si>
+    <t>PMS0034</t>
+  </si>
+  <si>
+    <t>Masterista Ice Shaken Lychee Tea 1000Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070060</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070061</t>
+  </si>
+  <si>
+    <t>BREAD YARD</t>
+  </si>
+  <si>
+    <t>PMS0108</t>
+  </si>
+  <si>
+    <t>Flavourista Syrup Caramel 750 Ml</t>
+  </si>
+  <si>
+    <t>PMS0141</t>
+  </si>
+  <si>
+    <t>Flavourista Syrup Strawberry 1000 Ml</t>
+  </si>
+  <si>
+    <t>PMS0156</t>
+  </si>
+  <si>
+    <t>Flavourista Syrup Hazelnut 1000 Ml</t>
+  </si>
+  <si>
+    <t>PMS0165</t>
+  </si>
+  <si>
+    <t>Flavourista Syrup Vanilla 1000 Ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070062</t>
+  </si>
+  <si>
+    <t>SRI RATIH COTTAGES</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070063</t>
+  </si>
+  <si>
+    <t>PT. TUNAS SAKA BALI (THE HUB BALI)</t>
+  </si>
+  <si>
+    <t>I Made Luih (Sanur)</t>
+  </si>
+  <si>
+    <t>PMS0038</t>
+  </si>
+  <si>
+    <t>Flavorista Chocolate base (1000Gr/Pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070064</t>
+  </si>
+  <si>
+    <t>PAS0056</t>
+  </si>
+  <si>
+    <t>Savis Earl Grey Tea 50 Tb Cover Alila</t>
+  </si>
+  <si>
+    <t>PAS0057</t>
+  </si>
+  <si>
+    <t>Savis English Breakfast Tea 50 Tb Cover Alila</t>
+  </si>
+  <si>
+    <t>PAS0058</t>
+  </si>
+  <si>
+    <t>Savis Chamomile Dream Tea 50 Tb Cover Alila</t>
+  </si>
+  <si>
+    <t>PAS0059</t>
+  </si>
+  <si>
+    <t>Savis Peppermint Tea 50 Tb Cover Alila</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070065</t>
+  </si>
+  <si>
+    <t>ALAM KUL KUL</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070066</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070067</t>
+  </si>
+  <si>
+    <t>HILTON HOTEL</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070068</t>
+  </si>
+  <si>
+    <t>POT0110</t>
+  </si>
+  <si>
+    <t>Bergold Shredded Pizza Topping Mozzarella</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070069</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070070</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070071</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070072</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070073</t>
+  </si>
+  <si>
+    <t>CV. FENNY BERSAMA</t>
+  </si>
+  <si>
+    <t>PMS0036</t>
+  </si>
+  <si>
+    <t>Artisan Pure Matcha (500Gr/Pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070074</t>
+  </si>
+  <si>
+    <t>AKSARI UBUD</t>
+  </si>
+  <si>
+    <t>CKP1S-020</t>
+  </si>
+  <si>
+    <t>Jinro Chamisul Soju 360 ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070075</t>
+  </si>
+  <si>
+    <t>MAMAKA</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070076</t>
+  </si>
+  <si>
+    <t>FEBRIS HOTEL</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070077</t>
+  </si>
+  <si>
+    <t>COFFEE CLUB BALI</t>
+  </si>
+  <si>
+    <t>ASS-LY-TB50</t>
+  </si>
+  <si>
+    <t>Lychee Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>ASS-MO-B</t>
+  </si>
+  <si>
+    <t>Manggo Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070078</t>
+  </si>
+  <si>
+    <t>THE VIRA BALI HOTEL</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070079</t>
+  </si>
+  <si>
+    <t>THE DUKE</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070080</t>
+  </si>
+  <si>
+    <t>PT. KREASI BALI PRIMA</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070081</t>
+  </si>
+  <si>
+    <t>WARUNG AYU PANDE PUTRI</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070082</t>
+  </si>
+  <si>
+    <t>TOKO RAHAYU</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070083</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070084</t>
+  </si>
+  <si>
+    <t>BALI RANI HOTEL</t>
+  </si>
+  <si>
+    <t>PMS0114</t>
+  </si>
+  <si>
+    <t>Masterista Cold Foam Sea Salt 500 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070085</t>
+  </si>
+  <si>
+    <t>PARADISUS BY MELIA NUSA DUA</t>
+  </si>
+  <si>
+    <t>PMS0161</t>
+  </si>
+  <si>
+    <t>Cocofreo Soft Ice Cream Belgian Chocolate 1000 Gr</t>
+  </si>
+  <si>
+    <t>PMS0162</t>
+  </si>
+  <si>
+    <t>Cocofreo Soft Ice Cream Vanilla 1000 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070086</t>
+  </si>
+  <si>
+    <t>FOOD GALLERIA</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070087</t>
+  </si>
+  <si>
+    <t>ASS-CH-TB50</t>
+  </si>
+  <si>
+    <t>Chamomile Dream @50Tb/Box</t>
+  </si>
+  <si>
+    <t>ASS-EBT</t>
+  </si>
+  <si>
+    <t>English Breakfast@50TB/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070088</t>
+  </si>
+  <si>
+    <t>PT. ADIKARYA PANGAN FRESHINDO</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070089</t>
+  </si>
+  <si>
+    <t>MAURI RESTAURANT</t>
   </si>
   <si>
     <t>POT0046</t>
@@ -105,19 +1104,43 @@
     <t>Australian Butter Unsalted</t>
   </si>
   <si>
-    <t>SO-KU/2608/070005</t>
-  </si>
-  <si>
-    <t>BADUNG  - Jimbaran Uluwatu</t>
-  </si>
-  <si>
-    <t>DRY</t>
-  </si>
-  <si>
-    <t>PIZZERIA ITALIA LABUAN SAIT</t>
-  </si>
-  <si>
-    <t>Juni</t>
+    <t>SO-KU/2609/070090</t>
+  </si>
+  <si>
+    <t>PENJUALAN CASH</t>
+  </si>
+  <si>
+    <t>Management Bali</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070091</t>
+  </si>
+  <si>
+    <t>TAMAN DEDARI UBUD</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070092</t>
+  </si>
+  <si>
+    <t>AKMANI HOTEL</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070093</t>
+  </si>
+  <si>
+    <t>BALI MANDIRA</t>
+  </si>
+  <si>
+    <t>PAL0003</t>
+  </si>
+  <si>
+    <t>Isabi Smoked Salmon Slice 1Kg/Pack</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070094</t>
+  </si>
+  <si>
+    <t>TAVERNA TOSCANA</t>
   </si>
   <si>
     <t>POT0120</t>
@@ -129,742 +1152,61 @@
     <t>GLN</t>
   </si>
   <si>
-    <t>SO-KU/2608/070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denpasar  - Selatan </t>
-  </si>
-  <si>
-    <t>KEDAI KOPI KOKO</t>
-  </si>
-  <si>
-    <t>I MADE LUIH</t>
-  </si>
-  <si>
-    <t>PMS0026</t>
-  </si>
-  <si>
-    <t>Masterista Dark Chocolate 800Gr</t>
-  </si>
-  <si>
-    <t>POU</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Kuta </t>
-  </si>
-  <si>
-    <t>ZEEN COFFEE</t>
-  </si>
-  <si>
-    <t>PMS0037</t>
-  </si>
-  <si>
-    <t>Flavorista Red Velvet (1000Gr/Pack)</t>
-  </si>
-  <si>
-    <t>PACK</t>
-  </si>
-  <si>
-    <t>PMS0134</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Salted Caramel 850 ML</t>
-  </si>
-  <si>
-    <t>BTL</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070009</t>
-  </si>
-  <si>
-    <t>ALILA HOTEL SEMINYAK</t>
-  </si>
-  <si>
-    <t>Vacant Hotel Seminyak Kuta</t>
-  </si>
-  <si>
-    <t>PAS0056</t>
-  </si>
-  <si>
-    <t>Savis Earl Grey Tea 50 Tb Cover Alila</t>
-  </si>
-  <si>
-    <t>BOX</t>
-  </si>
-  <si>
-    <t>PAS0057</t>
-  </si>
-  <si>
-    <t>Savis English Breakfast Tea 50 Tb Cover Alila</t>
-  </si>
-  <si>
-    <t>PAS0058</t>
-  </si>
-  <si>
-    <t>Savis Chamomile Dream Tea 50 Tb Cover Alila</t>
-  </si>
-  <si>
-    <t>PAS0059</t>
-  </si>
-  <si>
-    <t>Savis Peppermint Tea 50 Tb Cover Alila</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070010</t>
-  </si>
-  <si>
-    <t>Denpasar  - Sanur, Ketewel</t>
-  </si>
-  <si>
-    <t>BAKERY PETIT PARIS (PT. CIPTA RASA MULTINDO)</t>
-  </si>
-  <si>
-    <t>I Made Luih (Sanur)</t>
-  </si>
-  <si>
-    <t>PAA0001</t>
-  </si>
-  <si>
-    <t>Bergold Mozzarella Block</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070011</t>
-  </si>
-  <si>
-    <t>BALI CIAMIK SORO</t>
-  </si>
-  <si>
-    <t>Wira</t>
-  </si>
-  <si>
-    <t>CKP1S-160</t>
-  </si>
-  <si>
-    <t>Daebak Soju Mango @360ml/btl</t>
-  </si>
-  <si>
-    <t>CKP1S-164</t>
-  </si>
-  <si>
-    <t>Daebak Soju Lychee @360ml/btl</t>
-  </si>
-  <si>
-    <t>PJS0004</t>
-  </si>
-  <si>
-    <t>Daebak Soju Strawberry @360ml/btl</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070012</t>
-  </si>
-  <si>
-    <t>GRAND MERCURE SEMINYAK</t>
-  </si>
-  <si>
-    <t>POT0038</t>
-  </si>
-  <si>
-    <t>Premium Straight Cut 2Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070015</t>
-  </si>
-  <si>
-    <t>BREAD YARD</t>
-  </si>
-  <si>
-    <t>POS0024</t>
-  </si>
-  <si>
-    <t>O Sole Pomodori Pelati Peeled Tomatoes 2.5Kg</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Canggu </t>
-  </si>
-  <si>
-    <t>LIMA BAY RESTAURANT</t>
-  </si>
-  <si>
-    <t>Taufik</t>
-  </si>
-  <si>
-    <t>PMS0178</t>
-  </si>
-  <si>
-    <t>Masterista Ceremonial Pure Matcha Powder 500 Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070017</t>
-  </si>
-  <si>
-    <t>Gianyar  - Ubud</t>
-  </si>
-  <si>
-    <t>IBU SUSU UBUD</t>
-  </si>
-  <si>
-    <t>Picrom Stalyon</t>
-  </si>
-  <si>
-    <t>PMS0036</t>
-  </si>
-  <si>
-    <t>Artisan Pure Matcha (500Gr/Pack)</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070018</t>
-  </si>
-  <si>
-    <t>HIDE AWAY BEANS &amp; BOOZE</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070019</t>
-  </si>
-  <si>
-    <t>ITANA COFFEE AND EATERY</t>
-  </si>
-  <si>
-    <t>PMS0033</t>
-  </si>
-  <si>
-    <t>Masterista Ice Shaken Lemon Tea 1000Gr</t>
-  </si>
-  <si>
-    <t>PMS0034</t>
-  </si>
-  <si>
-    <t>Masterista Ice Shaken Lychee Tea 1000Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070020</t>
-  </si>
-  <si>
-    <t>M&amp;M CATERING</t>
-  </si>
-  <si>
-    <t>Eka</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070023</t>
-  </si>
-  <si>
-    <t>ZERO 4 KARAOKE</t>
-  </si>
-  <si>
-    <t>PIF0012</t>
-  </si>
-  <si>
-    <t>Pristine Classic Cooking Cream 1 Lt</t>
-  </si>
-  <si>
-    <t>LTR</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070024</t>
-  </si>
-  <si>
-    <t>Gianyar  - Gianyar</t>
-  </si>
-  <si>
-    <t>NOVOTEL BALI UBUD RESORT</t>
-  </si>
-  <si>
-    <t>PAS0041</t>
-  </si>
-  <si>
-    <t>Maestro FF 10x10mm Straight Cut 2.5 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070025</t>
-  </si>
-  <si>
-    <t>COPENHAGEN CAFE BERAWA</t>
-  </si>
-  <si>
-    <t>Dewi Kristiani</t>
-  </si>
-  <si>
-    <t>PEA0005</t>
-  </si>
-  <si>
-    <t>Gold Box Melange Butter MP331 5 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070026</t>
-  </si>
-  <si>
-    <t>PT. SSP TAURUS GEMILANG INDONESIA</t>
-  </si>
-  <si>
-    <t>PEA0010</t>
-  </si>
-  <si>
-    <t>Gold Box Extra Butter MP341 1 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070027</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070028</t>
-  </si>
-  <si>
-    <t>ASS-CH-TB50</t>
-  </si>
-  <si>
-    <t>Chamomile Dream @50Tb/Box</t>
-  </si>
-  <si>
-    <t>ASS-PGT</t>
-  </si>
-  <si>
-    <t>Pure Green Tea @50TB/Box</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070029</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070030</t>
-  </si>
-  <si>
-    <t>BADUNG  - NusaDua</t>
-  </si>
-  <si>
-    <t>RITZ CARLTON</t>
-  </si>
-  <si>
-    <t>Monica</t>
-  </si>
-  <si>
-    <t>PAL0003</t>
-  </si>
-  <si>
-    <t>Isabi Smoked Salmon Slice 1Kg/Pack</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070031</t>
-  </si>
-  <si>
-    <t>FINNS BEACH CLUB</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070032</t>
-  </si>
-  <si>
-    <t>150226</t>
-  </si>
-  <si>
-    <t>Belly Skinless Premium (2.5Kg/Pack)</t>
-  </si>
-  <si>
-    <t>MRD1318A</t>
-  </si>
-  <si>
-    <t>MAMAS BELLY RIND ON SB OUT (SKIN ON) 3-5KG/PACK</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denpasar  - Timur </t>
-  </si>
-  <si>
-    <t>S.O FROZEN</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070034</t>
-  </si>
-  <si>
-    <t>THE LAGUNA</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070036</t>
-  </si>
-  <si>
-    <t>DAPUR SEMBILAN FROZEN FOOD</t>
-  </si>
-  <si>
-    <t>PSJ0020</t>
-  </si>
-  <si>
-    <t>Off Cut 500 Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070037</t>
-  </si>
-  <si>
-    <t>PENINSULA BAY RESORT</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070038</t>
-  </si>
-  <si>
-    <t>PAS0036</t>
-  </si>
-  <si>
-    <t>Crr Rock'n Hash Brown Triangular 2.5Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070039</t>
-  </si>
-  <si>
-    <t>ROYAL TULIP SPRINGHILL RESORT JIMBARAN</t>
-  </si>
-  <si>
-    <t>PIF0011</t>
-  </si>
-  <si>
-    <t>Pristine Classic Whip Topping 1 Lt</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070040</t>
-  </si>
-  <si>
-    <t>BLEND CAFE</t>
-  </si>
-  <si>
-    <t>ASS-EBT</t>
-  </si>
-  <si>
-    <t>English Breakfast@50TB/Box</t>
-  </si>
-  <si>
-    <t>ASS-EGT</t>
-  </si>
-  <si>
-    <t>Earl Grey @50TB/Box</t>
-  </si>
-  <si>
-    <t>ASS-POT</t>
-  </si>
-  <si>
-    <t>Pure Olong Tea @50Tb/box</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070041</t>
-  </si>
-  <si>
-    <t>PIZZERIA ITALIA UNGASAN</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070042</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070043</t>
-  </si>
-  <si>
-    <t>DOM BY DOPPIO</t>
-  </si>
-  <si>
-    <t>PMS0028</t>
-  </si>
-  <si>
-    <t>Masterista Taro Expecta 800Gr</t>
-  </si>
-  <si>
-    <t>PMS0132</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Vanilla Tradition 850ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070044</t>
-  </si>
-  <si>
-    <t>ZIN CAFE CANGGU</t>
-  </si>
-  <si>
-    <t>PMS0027</t>
-  </si>
-  <si>
-    <t>Masterista Red Velvet Expecta 800Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070045</t>
-  </si>
-  <si>
-    <t>PT. SOEJASCH BALI</t>
-  </si>
-  <si>
-    <t>Management Bali</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070048</t>
-  </si>
-  <si>
-    <t>MAMAKA</t>
-  </si>
-  <si>
-    <t>POT0110</t>
-  </si>
-  <si>
-    <t>Bergold Shredded Pizza Topping Mozzarella</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070049</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070050</t>
-  </si>
-  <si>
-    <t>W HOTEL</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070051</t>
-  </si>
-  <si>
-    <t>UMANE KEROBOKAN</t>
-  </si>
-  <si>
-    <t>PMS0130</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Classic Caramel 850ml</t>
-  </si>
-  <si>
-    <t>PMS0131</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Tropical Lychee 850 Ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070052</t>
-  </si>
-  <si>
-    <t>RETAIL DAS BISTRO</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070054</t>
-  </si>
-  <si>
-    <t>NINE MART</t>
-  </si>
-  <si>
-    <t>Ni Ketut Sriasih (MT)</t>
-  </si>
-  <si>
-    <t>CKP1S-159</t>
-  </si>
-  <si>
-    <t>Daebak Soju Lemon @360ml/btl</t>
-  </si>
-  <si>
-    <t>CKP1S-163</t>
-  </si>
-  <si>
-    <t>Daebak Soju Peach @360ml/btl</t>
-  </si>
-  <si>
-    <t>CKP1S-165</t>
-  </si>
-  <si>
-    <t>Daebak Soju Original 360ml</t>
-  </si>
-  <si>
-    <t>CKP1S-181</t>
-  </si>
-  <si>
-    <t>Daebak Soju Grape 360ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070055</t>
+    <t>SO-KU/2609/070095</t>
+  </si>
+  <si>
+    <t>TENTANG KOPI KEROBOKAN</t>
+  </si>
+  <si>
+    <t>POT0039</t>
+  </si>
+  <si>
+    <t>Premium Spicy Wedges 2.5 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070096</t>
   </si>
   <si>
     <t>MAMAS GERMAN REST.</t>
   </si>
   <si>
-    <t>SO-KU/2608/070056</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070063</t>
-  </si>
-  <si>
-    <t>ANATHERA RESORT KUTA</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070064</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070066</t>
-  </si>
-  <si>
-    <t>BELLA ITALIAN GRAND MAS</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070068</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denpasar  - Barat </t>
-  </si>
-  <si>
-    <t>ROUMS COFE</t>
-  </si>
-  <si>
-    <t>PAS0015</t>
-  </si>
-  <si>
-    <t>Crr Rock'n Super Crispy Jakets Spicy Wedges 10Kg/Ctn</t>
-  </si>
-  <si>
-    <t>KTN</t>
-  </si>
-  <si>
-    <t>PAS0027</t>
-  </si>
-  <si>
-    <t>Maestro FF 10x10mm Straight Cut 10Kg/Ctn</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070071</t>
-  </si>
-  <si>
-    <t>HILTON HOTEL</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070072</t>
-  </si>
-  <si>
-    <t>VOUK HOTEL</t>
-  </si>
-  <si>
-    <t>PMS0093</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Strawberry 850 Ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070073</t>
-  </si>
-  <si>
-    <t>THE DUKE</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070074</t>
-  </si>
-  <si>
-    <t>COFFEE PHORA</t>
-  </si>
-  <si>
-    <t>PMS0183</t>
-  </si>
-  <si>
-    <t>Masterista Bitter Dark Chocolate (100% Pure Chocolate) 500 Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070075</t>
-  </si>
-  <si>
-    <t>WASABI RESTAURANT PERERENAN</t>
-  </si>
-  <si>
-    <t>ASS-JVJ</t>
-  </si>
-  <si>
-    <t>Javanese Jasmine Tea @50TB/Box</t>
-  </si>
-  <si>
-    <t>ASS-MO-B</t>
-  </si>
-  <si>
-    <t>Manggo Tea @50TB/Box</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070078</t>
-  </si>
-  <si>
-    <t>KYND COMMUNITY BALI</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070079</t>
-  </si>
-  <si>
-    <t>THE BLUE DOOR</t>
-  </si>
-  <si>
-    <t>POS0026</t>
-  </si>
-  <si>
-    <t>O Sole Olive Nere Denocciolate 4.1 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070080</t>
-  </si>
-  <si>
-    <t>FOLD CANGGU</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">East Bali  - Klungkung </t>
-  </si>
-  <si>
-    <t>GEP'S DELI ( TOKO SURYANTI NUSA )</t>
-  </si>
-  <si>
-    <t>PJS0008</t>
-  </si>
-  <si>
-    <t>ANI Hijau 580 Ml</t>
-  </si>
-  <si>
-    <t>PJS0009</t>
-  </si>
-  <si>
-    <t>ANI Merah 580 Ml</t>
-  </si>
-  <si>
-    <t>PJS0010</t>
-  </si>
-  <si>
-    <t>ANI Pink 580 Ml</t>
-  </si>
-  <si>
-    <t>PJS0011</t>
-  </si>
-  <si>
-    <t>ANI Lychee 580 Ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070082</t>
-  </si>
-  <si>
-    <t>TRIPLE EGG RESTAURANT</t>
-  </si>
-  <si>
-    <t>PMS0144</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Peach 850ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070085</t>
-  </si>
-  <si>
-    <t>FRANKIES BAR AND GRILL</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070086</t>
-  </si>
-  <si>
-    <t>SO-KU/2608/070087</t>
+    <t>SO-KU/2609/070097</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070098</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070099</t>
+  </si>
+  <si>
+    <t>DAS BISTRO</t>
+  </si>
+  <si>
+    <t>ASS-JVG</t>
+  </si>
+  <si>
+    <t>Java Ginger @50TB/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2609/070100</t>
+  </si>
+  <si>
+    <t>PAS0026</t>
+  </si>
+  <si>
+    <t>Crr Rock'n Batter Skin On Fries 9x9mm 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>POT0036</t>
+  </si>
+  <si>
+    <t>Premium Spicy Wedges 4x2.5 Kg</t>
   </si>
   <si>
     <t>KET</t>
   </si>
   <si>
-    <t>FULFILLED</t>
+    <t xml:space="preserve"> FULFILLED</t>
   </si>
   <si>
     <t>UNFULFILLED</t>
@@ -1485,10 +1827,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M104" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="13">
-  <autoFilter ref="A1:M104"/>
-  <sortState ref="A2:M104">
-    <sortCondition ref="I1:I104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M150" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="13">
+  <autoFilter ref="A1:M150"/>
+  <sortState ref="A2:M150">
+    <sortCondition ref="I1:I150"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" name="No. Urut" dataDxfId="12"/>
@@ -1775,17 +2117,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="8" customWidth="1"/>
     <col min="4" max="4" width="21.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="8" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11" style="8" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" style="8" customWidth="1"/>
     <col min="9" max="9" width="11" style="8" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="8" customWidth="1"/>
@@ -1831,212 +2173,212 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>279</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="3">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B5" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="3">
-        <v>4</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="3">
-        <v>4</v>
-      </c>
-      <c r="M3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="3">
-        <v>5</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="3">
-        <v>5</v>
-      </c>
-      <c r="M4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="15">
-        <v>6</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>281</v>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="15">
-        <v>9</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>281</v>
+        <v>46</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="3">
+        <v>5</v>
+      </c>
+      <c r="M6" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2059,455 +2401,455 @@
         <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="3">
+        <v>2</v>
+      </c>
+      <c r="M7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="F8" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="15">
-        <v>15</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="15">
-        <v>0</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="15">
-        <v>18</v>
-      </c>
-      <c r="K8" s="14" t="s">
+      <c r="I8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="15">
+        <v>69</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="3">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="15">
-        <v>0</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>281</v>
+      <c r="L9" s="3">
+        <v>30</v>
+      </c>
+      <c r="M9" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="3">
+        <v>5</v>
+      </c>
+      <c r="M10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-      <c r="M10" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J11" s="3">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L11" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
+      <c r="A12" s="12">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46273</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L12" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46242</v>
+      <c r="A13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="3">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="3">
         <v>1</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L13" s="3">
+      <c r="K14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="3">
         <v>1</v>
       </c>
-      <c r="M13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="M14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" s="3">
-        <v>2</v>
-      </c>
-      <c r="M14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="I15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2</v>
-      </c>
-      <c r="M15" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L16" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="3">
+        <v>5</v>
+      </c>
+      <c r="M17" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>105</v>
@@ -2516,511 +2858,511 @@
         <v>106</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L18" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M18" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>108</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="3">
-        <v>4</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L19" s="3">
-        <v>4</v>
-      </c>
-      <c r="M19" t="s">
-        <v>280</v>
+      <c r="H19" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="15">
+        <v>1</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46242</v>
+      <c r="A20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="15">
-        <v>4</v>
-      </c>
-      <c r="K20" s="14" t="s">
+      <c r="I20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L20" s="15">
+      <c r="H21" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="15">
+        <v>1</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="15">
         <v>0</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="M21" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="3">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J22" s="3">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="3">
-        <v>36</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L23" s="3">
-        <v>36</v>
-      </c>
-      <c r="M23" t="s">
-        <v>280</v>
+        <v>120</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="15">
+        <v>3</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J24" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L24" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M24" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>31</v>
-      </c>
-      <c r="B25" s="2">
-        <v>46242</v>
+      <c r="A25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3">
         <v>6</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L25" s="3">
         <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J26" s="3">
         <v>1</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
+      <c r="A27" s="12">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46273</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1</v>
-      </c>
-      <c r="M27" t="s">
-        <v>280</v>
+        <v>114</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="15">
+        <v>3</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>17</v>
+      <c r="A28" s="12">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46273</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="M28" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L29" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="M29" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
-        <v>35</v>
-      </c>
-      <c r="B30" s="2">
-        <v>46242</v>
+      <c r="A30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L30" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="M30" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -3043,95 +3385,95 @@
         <v>17</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L31" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="M31" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
-        <v>36</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46242</v>
+      <c r="A32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L32" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="M32" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
-        <v>37</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46242</v>
+      <c r="A33" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3">
         <v>20</v>
@@ -3143,48 +3485,48 @@
         <v>20</v>
       </c>
       <c r="M33" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
-        <v>41</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46242</v>
+      <c r="A34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="15">
-        <v>2</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L34" s="15">
-        <v>0</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>281</v>
+        <v>166</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="3">
+        <v>20</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="3">
+        <v>20</v>
+      </c>
+      <c r="M34" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -3207,312 +3549,312 @@
         <v>17</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="3">
+        <v>12</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="3">
+        <v>12</v>
+      </c>
+      <c r="M35" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="3">
+        <v>12</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="3">
+        <v>12</v>
+      </c>
+      <c r="M36" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="15">
+        <v>12</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
         <v>29</v>
       </c>
-      <c r="J35" s="3">
-        <v>4</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L35" s="3">
-        <v>4</v>
-      </c>
-      <c r="M35" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
+      <c r="B38" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="3">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="3">
-        <v>6</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L36" s="3">
-        <v>6</v>
-      </c>
-      <c r="M36" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>43</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" s="3">
-        <v>6</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L37" s="3">
-        <v>3</v>
-      </c>
-      <c r="M37" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" s="3">
-        <v>6</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="L38" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M38" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>17</v>
+      <c r="A39" s="12">
+        <v>30</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46273</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L39" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M39" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>17</v>
+      <c r="A40" s="12">
+        <v>31</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46273</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="L40" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M40" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>17</v>
+      <c r="A41" s="12">
+        <v>32</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46273</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J41" s="3">
         <v>6</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L41" s="3">
         <v>6</v>
       </c>
       <c r="M41" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>17</v>
+      <c r="A42" s="12">
+        <v>34</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46273</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>190</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42" s="15">
-        <v>6</v>
-      </c>
-      <c r="K42" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L42" s="15">
-        <v>0</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>281</v>
+      <c r="L42" s="3">
+        <v>3</v>
+      </c>
+      <c r="M42" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -3535,66 +3877,66 @@
         <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L43" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M43" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
-        <v>44</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46242</v>
+      <c r="A44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="L44" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M44" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -3617,312 +3959,312 @@
         <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="L45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M45" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>49</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46242</v>
+      <c r="A46" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>225</v>
+        <v>17</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L46" s="3">
         <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B47" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>238</v>
+        <v>69</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>239</v>
+        <v>70</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L47" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M47" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>17</v>
+      <c r="A48" s="12">
+        <v>39</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46273</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L48" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M48" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>17</v>
+      <c r="A49" s="12">
+        <v>40</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46273</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>214</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J49" s="15">
-        <v>2</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L49" s="15">
-        <v>0</v>
-      </c>
-      <c r="M49" s="16" t="s">
-        <v>281</v>
+        <v>69</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="3">
+        <v>36</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="3">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B50" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>43</v>
+        <v>216</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J50" s="3">
         <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L50" s="3">
         <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
-        <v>54</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46242</v>
+      <c r="A51" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>242</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>244</v>
+        <v>88</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
-        <v>55</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46242</v>
+      <c r="A52" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>246</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J52" s="3">
         <v>1</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L52" s="3">
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -3945,230 +4287,230 @@
         <v>17</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J53" s="3">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L53" s="3">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>17</v>
+      <c r="A54" s="12">
+        <v>44</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46273</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>17</v>
+        <v>234</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>17</v>
+        <v>235</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>251</v>
+        <v>70</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="L54" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M54" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B55" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J55" s="3">
         <v>1</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="L55" s="3">
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B56" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>256</v>
+        <v>69</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>257</v>
+        <v>70</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="L56" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M56" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B57" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>88</v>
+        <v>246</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="L57" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M57" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B58" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J58" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L58" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -4191,66 +4533,66 @@
         <v>17</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J59" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L59" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M59" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>17</v>
+      <c r="A60" s="12">
+        <v>55</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46273</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J60" s="15">
-        <v>10</v>
-      </c>
-      <c r="K60" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L60" s="15">
-        <v>0</v>
-      </c>
-      <c r="M60" s="16" t="s">
-        <v>281</v>
+        <v>218</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="3">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60" s="3">
+        <v>5</v>
+      </c>
+      <c r="M60" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -4273,25 +4615,25 @@
         <v>17</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>213</v>
+        <v>88</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J61" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L61" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -4314,25 +4656,25 @@
         <v>17</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J62" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L62" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M62" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -4355,25 +4697,25 @@
         <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J63" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L63" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M63" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -4396,66 +4738,66 @@
         <v>17</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J64" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L64" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M64" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>17</v>
+      <c r="A65" s="12">
+        <v>57</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46273</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J65" s="3">
-        <v>12</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L65" s="3">
-        <v>10</v>
-      </c>
-      <c r="M65" t="s">
-        <v>280</v>
+        <v>272</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="15">
+        <v>3</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L65" s="15">
+        <v>0</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -4478,189 +4820,189 @@
         <v>17</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J66" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L66" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M66" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="12">
-        <v>60</v>
-      </c>
-      <c r="B67" s="2">
-        <v>46242</v>
+      <c r="A67" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>271</v>
+        <v>17</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="L67" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M67" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
-        <v>62</v>
-      </c>
-      <c r="B68" s="2">
-        <v>46242</v>
+      <c r="A68" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>261</v>
+        <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>262</v>
+        <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J68" s="15">
-        <v>5</v>
-      </c>
-      <c r="K68" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L68" s="15">
-        <v>0</v>
-      </c>
-      <c r="M68" s="16" t="s">
-        <v>281</v>
+        <v>278</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J68" s="3">
+        <v>3</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L68" s="3">
+        <v>3</v>
+      </c>
+      <c r="M68" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>17</v>
+      <c r="A69" s="12">
+        <v>59</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46273</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>17</v>
+        <v>282</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>283</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L69" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M69" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>17</v>
+      <c r="A70" s="12">
+        <v>60</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46273</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>17</v>
+        <v>287</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J70" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="L70" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M70" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -4683,25 +5025,25 @@
         <v>17</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="I71" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J71" s="15">
-        <v>1</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L71" s="15">
-        <v>0</v>
-      </c>
-      <c r="M71" s="16" t="s">
-        <v>281</v>
+        <v>290</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J71" s="3">
+        <v>10</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L71" s="3">
+        <v>10</v>
+      </c>
+      <c r="M71" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -4724,763 +5066,763 @@
         <v>17</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="L72" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M72" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="12">
-        <v>63</v>
-      </c>
-      <c r="B73" s="2">
-        <v>46242</v>
+      <c r="A73" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>278</v>
+        <v>17</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>261</v>
+        <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>262</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I73" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J73" s="15">
-        <v>10</v>
-      </c>
-      <c r="K73" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L73" s="15">
-        <v>0</v>
-      </c>
-      <c r="M73" s="16" t="s">
-        <v>281</v>
+        <v>294</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" s="3">
+        <v>9</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L73" s="3">
+        <v>9</v>
+      </c>
+      <c r="M73" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="B74" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" s="3">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L74" s="3">
+        <v>2</v>
+      </c>
+      <c r="M74" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" s="3">
         <v>12</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" s="3">
-        <v>20</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L74" s="3">
-        <v>20</v>
-      </c>
-      <c r="M74" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="12">
-        <v>2</v>
-      </c>
-      <c r="B75" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J75" s="3">
-        <v>25</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="L75" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M75" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="B76" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J76" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="L76" s="3">
-        <v>26.079899999999999</v>
+        <v>6</v>
       </c>
       <c r="M76" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="B77" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J77" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L77" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M77" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="B78" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>115</v>
+        <v>307</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>116</v>
+        <v>240</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>117</v>
+        <v>300</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>96</v>
+        <v>242</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J78" s="15">
-        <v>5</v>
-      </c>
-      <c r="K78" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="L78" s="15">
-        <v>0</v>
-      </c>
-      <c r="M78" s="16" t="s">
-        <v>281</v>
+        <v>69</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J78" s="3">
+        <v>3</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L78" s="3">
+        <v>3</v>
+      </c>
+      <c r="M78" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B79" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>120</v>
+        <v>308</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>121</v>
+        <v>309</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>123</v>
+        <v>310</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>124</v>
+        <v>311</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L79" s="3">
-        <v>5.76</v>
+        <v>12</v>
       </c>
       <c r="M79" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="B80" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>43</v>
+        <v>246</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>127</v>
+        <v>314</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>128</v>
+        <v>315</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J80" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L80" s="3">
-        <v>11.57</v>
+        <v>5</v>
       </c>
       <c r="M80" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B81" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>129</v>
+        <v>320</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>43</v>
+        <v>216</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>126</v>
+        <v>321</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="L81" s="3">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="M81" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
-        <v>22</v>
-      </c>
-      <c r="B82" s="2">
-        <v>46242</v>
+      <c r="A82" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J82" s="3">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L82" s="3">
-        <v>5.16</v>
-      </c>
-      <c r="M82" t="s">
-        <v>280</v>
+        <v>322</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J82" s="15">
+        <v>2</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L82" s="15">
+        <v>0</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="12">
-        <v>23</v>
-      </c>
-      <c r="B83" s="2">
-        <v>46242</v>
+      <c r="A83" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="I83" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J83" s="15">
-        <v>6</v>
-      </c>
-      <c r="K83" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="L83" s="15">
-        <v>0</v>
-      </c>
-      <c r="M83" s="16" t="s">
-        <v>281</v>
+        <v>324</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B84" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>143</v>
+        <v>329</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J84" s="3">
+        <v>2</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L84" s="3">
+        <v>2</v>
+      </c>
+      <c r="M84" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <v>76</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J85" s="3">
         <v>30</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L84" s="3">
-        <v>32.03</v>
-      </c>
-      <c r="M84" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J85" s="3">
-        <v>10</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="L85" s="3">
-        <v>11.8</v>
+        <v>30</v>
       </c>
       <c r="M85" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>149</v>
+        <v>332</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>151</v>
+        <v>333</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>71</v>
+        <v>284</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L86" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M86" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="12">
-        <v>27</v>
-      </c>
-      <c r="B87" s="2">
-        <v>46242</v>
+      <c r="A87" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J87" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L87" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M87" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="B88" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>154</v>
+        <v>334</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>155</v>
+        <v>335</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J88" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="L88" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M88" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>17</v>
+      <c r="A89" s="12">
+        <v>80</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46273</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>17</v>
+        <v>337</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>156</v>
+        <v>339</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>157</v>
+        <v>340</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J89" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L89" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B90" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>160</v>
+        <v>341</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>159</v>
+        <v>342</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J90" s="3">
-        <v>7.56</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L90" s="3">
-        <v>6.54</v>
-      </c>
-      <c r="M90" t="s">
-        <v>280</v>
+        <v>343</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J90" s="15">
+        <v>5</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L90" s="15">
+        <v>0</v>
+      </c>
+      <c r="M90" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -5503,10 +5845,10 @@
         <v>17</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>161</v>
+        <v>345</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="I91" s="14" t="s">
         <v>14</v>
@@ -5515,546 +5857,2432 @@
         <v>5</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L91" s="15">
         <v>0</v>
       </c>
       <c r="M91" s="16" t="s">
-        <v>281</v>
+        <v>395</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B92" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>177</v>
+        <v>347</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>176</v>
+        <v>348</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>31</v>
+        <v>190</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J92" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L92" s="3">
-        <v>30.39</v>
+        <v>3</v>
       </c>
       <c r="M92" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="12">
-        <v>38</v>
-      </c>
-      <c r="B93" s="2">
-        <v>46242</v>
+      <c r="A93" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J93" s="3">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L93" s="3">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="M93" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B94" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>192</v>
+        <v>348</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>193</v>
+        <v>350</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>194</v>
+        <v>351</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J94" s="3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="L94" s="3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M94" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="12">
-        <v>40</v>
-      </c>
-      <c r="B95" s="2">
-        <v>46242</v>
+      <c r="A95" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>26</v>
+        <v>353</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J95" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="L95" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M95" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="12">
-        <v>45</v>
-      </c>
-      <c r="B96" s="2">
-        <v>46242</v>
+      <c r="A96" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>219</v>
+        <v>17</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J96" s="3">
-        <v>7</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L96" s="3">
-        <v>6.83</v>
-      </c>
-      <c r="M96" t="s">
-        <v>280</v>
+        <v>114</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J96" s="15">
+        <v>5</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L96" s="15">
+        <v>0</v>
+      </c>
+      <c r="M96" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B97" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>220</v>
+        <v>354</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>221</v>
+        <v>355</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J97" s="3">
-        <v>2.2999999999999998</v>
+        <v>10</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L97" s="3">
-        <v>2.1800000000000002</v>
+        <v>10</v>
       </c>
       <c r="M97" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>17</v>
+      <c r="A98" s="12">
+        <v>86</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46273</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>17</v>
+        <v>360</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
+        <v>361</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>17</v>
+        <v>362</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J98" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L98" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="12">
-        <v>47</v>
-      </c>
-      <c r="B99" s="2">
-        <v>46242</v>
+      <c r="A99" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>68</v>
+        <v>268</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J99" s="3">
-        <v>2.2999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L99" s="3">
-        <v>2.16</v>
+        <v>1</v>
       </c>
       <c r="M99" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="12">
-        <v>48</v>
-      </c>
-      <c r="B100" s="2">
-        <v>46242</v>
+      <c r="A100" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L100" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M100" t="s">
-        <v>280</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B101" s="2">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>226</v>
+        <v>365</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>228</v>
+        <v>366</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H101" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="I101" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J101" s="15">
-        <v>1</v>
-      </c>
-      <c r="K101" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L101" s="15">
-        <v>0</v>
-      </c>
-      <c r="M101" s="16" t="s">
-        <v>281</v>
+        <v>69</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J101" s="3">
+        <v>6</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L101" s="3">
+        <v>6</v>
+      </c>
+      <c r="M101" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>17</v>
+      <c r="A102" s="12">
+        <v>90</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46273</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>17</v>
+        <v>372</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H102" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I102" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J102" s="15">
-        <v>1</v>
-      </c>
-      <c r="K102" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L102" s="15">
-        <v>0</v>
-      </c>
-      <c r="M102" s="16" t="s">
-        <v>281</v>
+        <v>373</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J102" s="3">
+        <v>2</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="L102" s="3">
+        <v>2</v>
+      </c>
+      <c r="M102" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
+        <v>92</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J103" s="3">
+        <v>1</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L103" s="3">
+        <v>1</v>
+      </c>
+      <c r="M103" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <v>93</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J104" s="3">
+        <v>10</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L104" s="3">
+        <v>10</v>
+      </c>
+      <c r="M104" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J105" s="3">
+        <v>2</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L105" s="3">
+        <v>2</v>
+      </c>
+      <c r="M105" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <v>95</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J106" s="3">
+        <v>1</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L106" s="3">
+        <v>1</v>
+      </c>
+      <c r="M106" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I107" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J107" s="15">
+        <v>1</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L107" s="15">
+        <v>0</v>
+      </c>
+      <c r="M107" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <v>2</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" s="3">
+        <v>6</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108" s="3">
+        <v>6</v>
+      </c>
+      <c r="M108" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <v>6</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B103" s="2">
-        <v>46242</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D103" s="1" t="s">
+      <c r="D109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J109" s="3">
+        <v>6</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109" s="3">
+        <v>6</v>
+      </c>
+      <c r="M109" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" s="3">
+        <v>10</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L110" s="3">
+        <v>10</v>
+      </c>
+      <c r="M110" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="12">
+        <v>8</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" s="3">
+        <v>1</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L111" s="3">
+        <v>1</v>
+      </c>
+      <c r="M111" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" s="12">
+        <v>10</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J112" s="3">
+        <v>10</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L112" s="3">
+        <v>10</v>
+      </c>
+      <c r="M112" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J113" s="3">
+        <v>30</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L113" s="3">
+        <v>30</v>
+      </c>
+      <c r="M113" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="12">
+        <v>13</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" s="3">
+        <v>4</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L114" s="3">
+        <v>4</v>
+      </c>
+      <c r="M114" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="12">
+        <v>16</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" s="3">
+        <v>25</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L115" s="3">
+        <v>25</v>
+      </c>
+      <c r="M115" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="12">
+        <v>23</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="G116" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H116" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="I116" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" s="3">
+        <v>300</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L116" s="3">
+        <v>304.3999</v>
+      </c>
+      <c r="M116" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <v>25</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="I117" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J117" s="3">
+        <v>50</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L117" s="3">
+        <v>52.56</v>
+      </c>
+      <c r="M117" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="12">
+        <v>26</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J103" s="3">
+      <c r="D118" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" s="3">
+        <v>2</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L118" s="3">
+        <v>2</v>
+      </c>
+      <c r="M118" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="12">
+        <v>33</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J119" s="3">
+        <v>4</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L119" s="3">
+        <v>4.08</v>
+      </c>
+      <c r="M119" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="12">
+        <v>35</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J120" s="3">
+        <v>2</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L120" s="3">
+        <v>1.88</v>
+      </c>
+      <c r="M120" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="12">
+        <v>37</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J121" s="3">
         <v>10</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K121" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L121" s="3">
+        <v>10</v>
+      </c>
+      <c r="M121" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="12">
+        <v>38</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J122" s="3">
+        <v>15</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L122" s="3">
+        <v>15</v>
+      </c>
+      <c r="M122" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="12">
+        <v>42</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I123" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J123" s="15">
+        <v>10</v>
+      </c>
+      <c r="K123" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L123" s="15">
+        <v>0</v>
+      </c>
+      <c r="M123" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" s="3">
+        <v>10</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L124" s="3">
+        <v>10.4499</v>
+      </c>
+      <c r="M124" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="12">
+        <v>43</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J125" s="3">
+        <v>8</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L125" s="3">
+        <v>5.12</v>
+      </c>
+      <c r="M125" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="12">
+        <v>46</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J126" s="3">
+        <v>4</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L126" s="3">
+        <v>4</v>
+      </c>
+      <c r="M126" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="12">
+        <v>49</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J127" s="3">
+        <v>15</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L127" s="3">
+        <v>15.32</v>
+      </c>
+      <c r="M127" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="12">
+        <v>50</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J128" s="3">
         <v>20</v>
       </c>
-      <c r="L103" s="3">
-        <v>6.66</v>
-      </c>
-      <c r="M103" t="s">
+      <c r="K128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L128" s="3">
+        <v>20</v>
+      </c>
+      <c r="M128" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="12">
+        <v>51</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J129" s="3">
+        <v>6</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L129" s="3">
+        <v>2</v>
+      </c>
+      <c r="M129" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="12">
+        <v>52</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J130" s="3">
+        <v>15</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L130" s="3">
+        <v>15.25</v>
+      </c>
+      <c r="M130" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="12">
+        <v>53</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J131" s="3">
+        <v>5</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L131" s="3">
+        <v>5</v>
+      </c>
+      <c r="M131" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="12">
+        <v>56</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J132" s="3">
+        <v>8</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L132" s="3">
+        <v>4.32</v>
+      </c>
+      <c r="M132" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="12">
+        <v>58</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="13">
-        <v>61</v>
-      </c>
-      <c r="B104" s="6">
-        <v>46242</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I104" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J104" s="7">
+      <c r="D133" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J133" s="3">
         <v>5</v>
       </c>
-      <c r="K104" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L104" s="3">
+      <c r="K133" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L133" s="3">
+        <v>4.37</v>
+      </c>
+      <c r="M133" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="12">
+        <v>64</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J134" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L134" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="M134" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="12">
+        <v>65</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J135" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L135" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="M135" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="12">
+        <v>66</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J136" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L136" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M136" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="12">
+        <v>67</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J137" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L137" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M137" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="12">
+        <v>71</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J138" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L138" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M138" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="12">
+        <v>72</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J139" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L139" s="3">
+        <v>4.37</v>
+      </c>
+      <c r="M139" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="12">
+        <v>74</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L140" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M140" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="12">
+        <v>79</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" s="3">
+        <v>30</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L141" s="3">
+        <v>30</v>
+      </c>
+      <c r="M141" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" s="12">
+        <v>85</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" s="3">
+        <v>25</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L142" s="3">
+        <v>25</v>
+      </c>
+      <c r="M142" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="12">
+        <v>87</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" s="3">
+        <v>30</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L143" s="3">
+        <v>30</v>
+      </c>
+      <c r="M143" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" s="12">
+        <v>89</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J144" s="3">
+        <v>1</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L144" s="3">
+        <v>1</v>
+      </c>
+      <c r="M144" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="12">
+        <v>91</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" s="3">
+        <v>2</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L145" s="3">
+        <v>2</v>
+      </c>
+      <c r="M145" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H146" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I146" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J146" s="15">
+        <v>2</v>
+      </c>
+      <c r="K146" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L146" s="15">
+        <v>0</v>
+      </c>
+      <c r="M146" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" s="12">
+        <v>94</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J147" s="3">
+        <v>1</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L147" s="3">
+        <v>1</v>
+      </c>
+      <c r="M147" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="12">
+        <v>96</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="H148" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="I148" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" s="15">
+        <v>1</v>
+      </c>
+      <c r="K148" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="L148" s="15">
+        <v>0</v>
+      </c>
+      <c r="M148" s="16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" s="3">
+        <v>1</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L149" s="3">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" s="7">
         <v>5</v>
       </c>
-      <c r="M104" t="s">
-        <v>280</v>
+      <c r="K150" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L150" s="7">
+        <v>5</v>
+      </c>
+      <c r="M150" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
